--- a/data/trans_dic/IP2005-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2005-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que tienen los dientes sanos</t>
+          <t>Menores que tienen los dientes sanos (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,81; 94,22</t>
+          <t>85,81; 94,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>84,27; 93,37</t>
+          <t>84,24; 93,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,83; 96,71</t>
+          <t>88,66; 96,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83,77; 93,47</t>
+          <t>83,78; 93,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,88; 94,35</t>
+          <t>86,74; 94,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,1; 93,22</t>
+          <t>83,93; 92,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,54; 93,63</t>
+          <t>84,75; 93,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>84,43; 94,33</t>
+          <t>83,45; 94,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,94; 93,49</t>
+          <t>87,92; 93,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85,68; 92,13</t>
+          <t>86,13; 92,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88,41; 94,5</t>
+          <t>88,45; 94,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,81; 93,01</t>
+          <t>85,61; 92,86</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,68; 90,41</t>
+          <t>82,85; 90,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,4; 92,56</t>
+          <t>85,66; 92,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,56; 95,5</t>
+          <t>89,21; 95,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88,92; 95,49</t>
+          <t>89,35; 95,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>78,81; 86,87</t>
+          <t>78,6; 87,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,35; 92,92</t>
+          <t>86,3; 93,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,29; 94,97</t>
+          <t>89,05; 95,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>84,76; 92,3</t>
+          <t>84,61; 92,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,64; 87,52</t>
+          <t>82,05; 87,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86,92; 91,99</t>
+          <t>87,12; 91,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89,8; 94,4</t>
+          <t>90,25; 94,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>87,79; 92,98</t>
+          <t>88,0; 93,03</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,0; 93,7</t>
+          <t>86,12; 93,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,77; 93,61</t>
+          <t>86,2; 94,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91,04; 96,86</t>
+          <t>91,13; 97,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84,93; 94,4</t>
+          <t>85,64; 94,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,9; 96,1</t>
+          <t>88,96; 96,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,8; 94,16</t>
+          <t>86,78; 94,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,52; 93,86</t>
+          <t>85,9; 93,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83,5; 92,34</t>
+          <t>83,84; 92,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89,01; 94,09</t>
+          <t>88,99; 94,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>87,64; 93,18</t>
+          <t>87,52; 92,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89,49; 94,29</t>
+          <t>89,02; 94,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85,91; 92,49</t>
+          <t>86,13; 92,35</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,33; 92,09</t>
+          <t>84,75; 92,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,42; 94,58</t>
+          <t>87,53; 94,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,79; 95,28</t>
+          <t>88,41; 95,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72,51; 83,8</t>
+          <t>72,72; 83,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,96; 93,12</t>
+          <t>86,13; 93,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,04; 96,28</t>
+          <t>89,42; 95,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,61; 94,74</t>
+          <t>87,73; 94,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78,07; 88,23</t>
+          <t>77,85; 88,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,27; 91,88</t>
+          <t>86,34; 91,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89,99; 94,63</t>
+          <t>90,0; 94,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89,28; 94,28</t>
+          <t>89,42; 94,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,84; 85,02</t>
+          <t>77,36; 84,77</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,8; 90,72</t>
+          <t>86,87; 90,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,31; 92,24</t>
+          <t>88,19; 92,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,3; 94,61</t>
+          <t>91,45; 94,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,27; 89,93</t>
+          <t>85,5; 90,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,69; 90,79</t>
+          <t>86,73; 90,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,86; 92,5</t>
+          <t>88,92; 92,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,35; 92,87</t>
+          <t>89,16; 92,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,67; 90,08</t>
+          <t>85,44; 90,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,59; 90,24</t>
+          <t>87,41; 90,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89,25; 91,75</t>
+          <t>89,17; 91,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90,9; 93,33</t>
+          <t>90,94; 93,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,23; 89,35</t>
+          <t>86,17; 89,43</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen los dientes sanos (tasa de respuesta: 99,37%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>114446</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>119248</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>116194</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>103449</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>127283</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>125429</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>124362</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>123076</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>241729</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>244676</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>240556</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>226526</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>108348; 118863</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112179; 124224</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>109985; 119985</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>96780; 108345</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>121077; 131859</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>118313; 131057</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>117305; 129169</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>114119; 129135</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>233728; 248724</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>236112; 252681</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>232154; 247737</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>215980; 234266</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>161195</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>170702</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>179840</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>173475</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>169093</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>190658</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>194231</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>221689</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>330287</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>361360</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>374072</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>395163</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>153920; 168750</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>163452; 176553</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>172946; 184840</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>167000; 178059</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>159954; 177539</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>183032; 197581</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>187031; 199933</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>210214; 229607</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>319436; 341489</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>351002; 370453</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>364522; 381589</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>383104; 404975</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>115853</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>130671</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>137911</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>168763</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>129849</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>137856</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>143400</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>163020</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>245701</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>268527</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>281311</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>331783</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>110499; 120319</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>124700; 136107</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>133036; 141761</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>160994; 177311</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>123964; 133809</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>131408; 142817</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>136598; 149399</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>154010; 169898</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>238176; 252159</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>259151; 274991</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>271529; 287917</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>320141; 343273</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>173547</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>175868</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>177992</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>130864</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>176221</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>182032</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>174618</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>149306</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>349769</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>357899</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>352610</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>280171</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>165833; 180674</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167776; 181801</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170171; 183234</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>120801; 138778</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>168656; 182475</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>174460; 186966</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>167284; 180330</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>138465; 156977</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>338004; 358267</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>348121; 366099</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>342629; 360963</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>266091; 291602</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1749</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1771</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1829</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1633</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>565042</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>596489</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>611937</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>576551</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>602445</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>635974</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>636612</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>657092</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1167487</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1232463</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1248548</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1233643</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>552531; 576424</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>582311; 608271</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>600248; 621850</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>561306; 591304</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>588262; 613949</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>622104; 647771</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>622476; 648463</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>638014; 673197</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1148769; 1184449</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1212613; 1249917</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1231855; 1266165</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1209241; 1254989</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2005-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2005-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,81; 94,14</t>
+          <t>85,73; 94,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>84,24; 93,28</t>
+          <t>84,24; 93,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,66; 96,72</t>
+          <t>88,45; 96,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83,78; 93,79</t>
+          <t>84,25; 93,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,74; 94,46</t>
+          <t>86,12; 94,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,93; 92,97</t>
+          <t>83,93; 93,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,75; 93,32</t>
+          <t>85,07; 93,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83,45; 94,43</t>
+          <t>83,98; 94,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,92; 93,56</t>
+          <t>87,84; 93,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86,13; 92,17</t>
+          <t>85,65; 92,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88,45; 94,39</t>
+          <t>88,23; 94,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,61; 92,86</t>
+          <t>85,78; 93,09</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,85; 90,83</t>
+          <t>82,59; 90,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,66; 92,53</t>
+          <t>85,88; 92,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,21; 95,35</t>
+          <t>89,19; 95,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89,35; 95,27</t>
+          <t>89,31; 95,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>78,6; 87,24</t>
+          <t>78,51; 86,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,3; 93,16</t>
+          <t>85,88; 92,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,05; 95,19</t>
+          <t>89,35; 95,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>84,61; 92,42</t>
+          <t>84,75; 92,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82,05; 87,72</t>
+          <t>81,66; 87,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87,12; 91,95</t>
+          <t>86,92; 91,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90,25; 94,48</t>
+          <t>90,2; 94,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>88,0; 93,03</t>
+          <t>87,96; 93,13</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,12; 93,77</t>
+          <t>85,69; 94,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,2; 94,09</t>
+          <t>86,02; 94,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91,13; 97,11</t>
+          <t>91,13; 96,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85,64; 94,32</t>
+          <t>85,03; 94,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,96; 96,03</t>
+          <t>89,07; 96,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,78; 94,31</t>
+          <t>87,07; 94,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,9; 93,95</t>
+          <t>85,25; 93,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83,84; 92,49</t>
+          <t>83,67; 92,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>88,99; 94,21</t>
+          <t>88,95; 94,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>87,52; 92,87</t>
+          <t>87,74; 93,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89,02; 94,4</t>
+          <t>89,28; 94,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>86,13; 92,35</t>
+          <t>85,89; 92,17</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,75; 92,33</t>
+          <t>84,4; 92,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,53; 94,85</t>
+          <t>87,71; 94,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,41; 95,19</t>
+          <t>88,49; 95,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72,72; 83,54</t>
+          <t>72,99; 84,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,13; 93,18</t>
+          <t>85,87; 93,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,42; 95,83</t>
+          <t>89,38; 95,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,73; 94,57</t>
+          <t>86,71; 94,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>77,85; 88,26</t>
+          <t>78,58; 88,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,34; 91,51</t>
+          <t>86,42; 91,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90,0; 94,65</t>
+          <t>89,77; 94,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89,42; 94,21</t>
+          <t>89,16; 94,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,36; 84,77</t>
+          <t>77,32; 85,08</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,87; 90,63</t>
+          <t>86,62; 90,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,19; 92,12</t>
+          <t>88,22; 92,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,45; 94,74</t>
+          <t>91,5; 94,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,5; 90,07</t>
+          <t>85,57; 90,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,73; 90,52</t>
+          <t>86,82; 90,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,92; 92,59</t>
+          <t>88,93; 92,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,16; 92,88</t>
+          <t>89,27; 92,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,44; 90,15</t>
+          <t>85,44; 90,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,41; 90,12</t>
+          <t>87,33; 90,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89,17; 91,91</t>
+          <t>89,25; 91,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90,94; 93,48</t>
+          <t>90,8; 93,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,17; 89,43</t>
+          <t>86,4; 89,63</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>108348; 118863</t>
+          <t>108254; 118805</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>112179; 124224</t>
+          <t>112186; 124622</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109985; 119985</t>
+          <t>109723; 120071</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>96780; 108345</t>
+          <t>97320; 108226</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>121077; 131859</t>
+          <t>120208; 131691</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>118313; 131057</t>
+          <t>118317; 131216</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>117305; 129169</t>
+          <t>117739; 129344</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>114119; 129135</t>
+          <t>114855; 129466</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>233728; 248724</t>
+          <t>233518; 248048</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>236112; 252681</t>
+          <t>234788; 252302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>232154; 247737</t>
+          <t>231559; 247078</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>215980; 234266</t>
+          <t>216397; 234834</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>153920; 168750</t>
+          <t>153446; 167795</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>163452; 176553</t>
+          <t>163876; 177143</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>172946; 184840</t>
+          <t>172900; 184584</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>167000; 178059</t>
+          <t>166911; 178384</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>159954; 177539</t>
+          <t>159779; 176650</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>183032; 197581</t>
+          <t>182144; 196468</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>187031; 199933</t>
+          <t>187657; 199644</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>210214; 229607</t>
+          <t>210549; 229598</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>319436; 341489</t>
+          <t>317914; 340988</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>351002; 370453</t>
+          <t>350203; 369786</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>364522; 381589</t>
+          <t>364328; 381174</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>383104; 404975</t>
+          <t>382917; 405406</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>110499; 120319</t>
+          <t>109945; 120684</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>124700; 136107</t>
+          <t>124433; 136030</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133036; 141761</t>
+          <t>133030; 141184</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>160994; 177311</t>
+          <t>159850; 176982</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>123964; 133809</t>
+          <t>124110; 133886</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>131408; 142817</t>
+          <t>131853; 143202</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>136598; 149399</t>
+          <t>135571; 149372</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>154010; 169898</t>
+          <t>153710; 169589</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>238176; 252159</t>
+          <t>238068; 252030</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>259151; 274991</t>
+          <t>259794; 275606</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>271529; 287917</t>
+          <t>272301; 287812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>320141; 343273</t>
+          <t>319230; 342601</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>165833; 180674</t>
+          <t>165161; 180591</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>167776; 181801</t>
+          <t>168122; 181914</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>170171; 183234</t>
+          <t>170319; 183452</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>120801; 138778</t>
+          <t>121252; 139602</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>168656; 182475</t>
+          <t>168147; 182431</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>174460; 186966</t>
+          <t>174380; 186968</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>167284; 180330</t>
+          <t>165336; 179926</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>138465; 156977</t>
+          <t>139765; 156770</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>338004; 358267</t>
+          <t>338351; 359904</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>348121; 366099</t>
+          <t>347214; 366429</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>342629; 360963</t>
+          <t>341630; 360183</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>266091; 291602</t>
+          <t>265955; 292670</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>552531; 576424</t>
+          <t>550920; 577113</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>582311; 608271</t>
+          <t>582533; 607939</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>600248; 621850</t>
+          <t>600600; 621485</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561306; 591304</t>
+          <t>561769; 591434</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>588262; 613949</t>
+          <t>588853; 615466</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>622104; 647771</t>
+          <t>622114; 647513</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>622476; 648463</t>
+          <t>623220; 648223</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>638014; 673197</t>
+          <t>638033; 672062</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1148769; 1184449</t>
+          <t>1147811; 1183551</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1212613; 1249917</t>
+          <t>1213770; 1248925</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1231855; 1266165</t>
+          <t>1229970; 1263683</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1209241; 1254989</t>
+          <t>1212458; 1257706</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2005-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2005-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>88,97%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>89,85%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>90,02%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>90,64%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>89,55%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>93,67%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>89,55%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>88,97%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,85%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,73; 94,09</t>
+          <t>86,88; 94,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>84,24; 93,58</t>
+          <t>84,1; 93,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,45; 96,79</t>
+          <t>84,54; 93,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,25; 93,69</t>
+          <t>84,7; 94,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,12; 94,34</t>
+          <t>85,81; 94,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,93; 93,08</t>
+          <t>84,27; 93,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,07; 93,45</t>
+          <t>88,83; 96,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83,98; 94,67</t>
+          <t>83,53; 93,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,84; 93,3</t>
+          <t>87,94; 93,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85,65; 92,03</t>
+          <t>85,68; 92,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88,23; 94,14</t>
+          <t>88,41; 94,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,78; 93,09</t>
+          <t>85,87; 93,02</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83,09%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89,9%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>92,48%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89,43%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>86,76%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>89,46%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>92,77%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>92,82%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>83,09%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>89,9%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>92,48%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,59; 90,32</t>
+          <t>78,81; 86,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,88; 92,84</t>
+          <t>86,35; 92,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,19; 95,21</t>
+          <t>89,29; 94,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89,31; 95,44</t>
+          <t>84,81; 92,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>78,51; 86,8</t>
+          <t>82,68; 90,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,88; 92,64</t>
+          <t>85,4; 92,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,35; 95,05</t>
+          <t>89,56; 95,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>84,75; 92,42</t>
+          <t>88,58; 95,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,66; 87,59</t>
+          <t>81,64; 87,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86,92; 91,78</t>
+          <t>86,92; 91,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90,2; 94,37</t>
+          <t>89,8; 94,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>87,96; 93,13</t>
+          <t>87,78; 93,07</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>93,19%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>91,03%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>88,58%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>90,29%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>90,33%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>94,47%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>89,77%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,19%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,39%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>85,69; 94,06</t>
+          <t>88,9; 96,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,02; 94,04</t>
+          <t>86,8; 94,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91,13; 96,72</t>
+          <t>85,52; 93,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85,03; 94,15</t>
+          <t>83,5; 92,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89,07; 96,08</t>
+          <t>86,0; 93,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,07; 94,56</t>
+          <t>85,77; 93,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,25; 93,93</t>
+          <t>91,04; 96,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83,67; 92,32</t>
+          <t>83,43; 91,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>88,95; 94,16</t>
+          <t>89,01; 94,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>87,74; 93,08</t>
+          <t>87,64; 93,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89,28; 94,36</t>
+          <t>89,49; 94,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85,89; 92,17</t>
+          <t>84,85; 91,38</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>89,99%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>93,3%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>91,58%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>83,65%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>88,69%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>91,75%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>92,47%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>78,78%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>93,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,4; 92,29</t>
+          <t>85,96; 93,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,71; 94,91</t>
+          <t>90,04; 96,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,49; 95,31</t>
+          <t>87,61; 94,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72,99; 84,04</t>
+          <t>77,73; 88,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,87; 93,16</t>
+          <t>84,33; 92,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,38; 95,83</t>
+          <t>87,42; 94,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,71; 94,36</t>
+          <t>88,79; 95,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78,58; 88,14</t>
+          <t>72,2; 83,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,42; 91,93</t>
+          <t>86,27; 91,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89,77; 94,74</t>
+          <t>89,99; 94,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89,16; 94,0</t>
+          <t>89,28; 94,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,32; 85,08</t>
+          <t>77,47; 84,86</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>88,82%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>90,91%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>91,19%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>88,84%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>90,33%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>93,23%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>87,82%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>88,82%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>90,91%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>91,19%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,62; 90,74</t>
+          <t>86,69; 90,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,22; 92,07</t>
+          <t>88,86; 92,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,5; 94,68</t>
+          <t>89,35; 92,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,57; 90,09</t>
+          <t>85,52; 90,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,82; 90,74</t>
+          <t>86,8; 90,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,93; 92,56</t>
+          <t>88,31; 92,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,27; 92,85</t>
+          <t>91,3; 94,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,44; 90,0</t>
+          <t>84,68; 89,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,33; 90,05</t>
+          <t>87,59; 90,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89,25; 91,84</t>
+          <t>89,25; 91,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90,8; 93,29</t>
+          <t>90,9; 93,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,4; 89,63</t>
+          <t>85,92; 88,99</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>173</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>127283</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>125429</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>124362</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>110611</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>114446</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>119248</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>116194</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>103449</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>127283</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>125429</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>124362</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>123076</t>
+          <t>106992</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>226526</t>
+          <t>217602</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>108254; 118805</t>
+          <t>121278; 131697</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>112186; 124622</t>
+          <t>118564; 131411</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109723; 120071</t>
+          <t>117016; 129595</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>97320; 108226</t>
+          <t>104083; 116075</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>120208; 131691</t>
+          <t>108354; 118971</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>118317; 131216</t>
+          <t>112224; 124339</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>117739; 129344</t>
+          <t>110194; 119975</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>114855; 129466</t>
+          <t>99952; 111779</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>233518; 248048</t>
+          <t>233795; 248538</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>234788; 252302</t>
+          <t>234882; 252579</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>231559; 247078</t>
+          <t>232036; 248018</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>216397; 234834</t>
+          <t>208261; 225618</t>
         </is>
       </c>
     </row>
@@ -1722,37 +1722,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>289</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>250</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>169093</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>190658</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>194231</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>207421</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>161195</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>170702</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>179840</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>173475</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>169093</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>190658</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>194231</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>221689</t>
+          <t>168458</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>395163</t>
+          <t>375880</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>153446; 167795</t>
+          <t>160377; 176786</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>163876; 177143</t>
+          <t>183144; 197079</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>172900; 184584</t>
+          <t>187540; 199474</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>166911; 178384</t>
+          <t>196718; 214517</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>159779; 176650</t>
+          <t>153610; 167963</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>182144; 196468</t>
+          <t>162946; 176621</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>187657; 199644</t>
+          <t>173618; 185145</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>210549; 229598</t>
+          <t>160928; 173273</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>317914; 340988</t>
+          <t>317818; 340727</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>350203; 369786</t>
+          <t>350187; 370641</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>364328; 381174</t>
+          <t>362686; 381272</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>382917; 405406</t>
+          <t>363057; 384956</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>227</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>194</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>129849</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>137856</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>143400</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>148057</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>115853</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>130671</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>137911</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>168763</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>129849</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>137856</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>143400</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>163020</t>
+          <t>136397</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>331783</t>
+          <t>284454</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>109945; 120684</t>
+          <t>123877; 133902</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>124433; 136030</t>
+          <t>131447; 142598</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133030; 141184</t>
+          <t>136006; 149261</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>159850; 176982</t>
+          <t>139568; 154411</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>124110; 133886</t>
+          <t>110343; 120227</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>131853; 143202</t>
+          <t>124075; 135420</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>135571; 149372</t>
+          <t>132899; 141388</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>153710; 169589</t>
+          <t>129042; 142275</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>238068; 252030</t>
+          <t>238225; 251839</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>259794; 275606</t>
+          <t>259487; 275890</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>272301; 287812</t>
+          <t>272942; 287591</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>319230; 342601</t>
+          <t>273079; 294077</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>241</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>187</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>176221</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>182032</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>174618</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>139366</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>173547</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>175868</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>177992</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>130864</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>176221</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>182032</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>174618</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>149306</t>
+          <t>129739</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>280171</t>
+          <t>269106</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>165161; 180591</t>
+          <t>168327; 182353</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>168122; 181914</t>
+          <t>175667; 187852</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>170319; 183452</t>
+          <t>167060; 180656</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121252; 139602</t>
+          <t>129500; 146696</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>168147; 182431</t>
+          <t>165015; 180207</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>174380; 186968</t>
+          <t>167570; 181293</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>165336; 179926</t>
+          <t>170908; 183405</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>139765; 156770</t>
+          <t>119255; 138119</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>338351; 359904</t>
+          <t>337751; 359712</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>347214; 366429</t>
+          <t>348062; 365993</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>341630; 360183</t>
+          <t>342106; 361258</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>265955; 292670</t>
+          <t>257040; 281532</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>842</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>861</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>918</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>804</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>911</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>829</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>602445</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>635974</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>636612</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>605456</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>565042</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>596489</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>611937</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>576551</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>602445</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>635974</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>636612</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>657092</t>
+          <t>541586</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1233643</t>
+          <t>1147041</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>550920; 577113</t>
+          <t>588001; 615775</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>582533; 607939</t>
+          <t>621627; 647096</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>600600; 621485</t>
+          <t>623795; 648383</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561769; 591434</t>
+          <t>588897; 619965</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>588853; 615466</t>
+          <t>552078; 577011</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>622114; 647513</t>
+          <t>583154; 609046</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>623220; 648223</t>
+          <t>599300; 621013</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>638033; 672062</t>
+          <t>526008; 553879</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1147811; 1183551</t>
+          <t>1151246; 1186030</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1213770; 1248925</t>
+          <t>1213678; 1247739</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1229970; 1263683</t>
+          <t>1231256; 1264212</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1212458; 1257706</t>
+          <t>1125379; 1165551</t>
         </is>
       </c>
     </row>
